--- a/output_excel/5233595.xlsx
+++ b/output_excel/5233595.xlsx
@@ -568,7 +568,11 @@
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr">
@@ -620,7 +624,11 @@
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr">
@@ -672,7 +680,11 @@
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr">
